--- a/knowledge/frameworks/instagram-content/sample-canva-strategy-test.xlsx
+++ b/knowledge/frameworks/instagram-content/sample-canva-strategy-test.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AF2"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,140 +439,105 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Body1_PerfectIf</t>
+          <t>Body2_Heading</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Body2_Heading</t>
+          <t>Body2_P1</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>Body2_P1</t>
+          <t>Body2_P2</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
         <is>
-          <t>Body2_P2</t>
+          <t>Body3_Heading</t>
         </is>
       </c>
       <c r="I1" t="inlineStr">
         <is>
-          <t>Body2_PerfectIf</t>
+          <t>Body3_P1</t>
         </is>
       </c>
       <c r="J1" t="inlineStr">
         <is>
-          <t>Body3_Heading</t>
+          <t>Body3_P2</t>
         </is>
       </c>
       <c r="K1" t="inlineStr">
         <is>
-          <t>Body3_P1</t>
+          <t>Body4_Heading</t>
         </is>
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Body3_P2</t>
+          <t>Body4_P1</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Body3_PerfectIf</t>
+          <t>Body4_P2</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Body4_Heading</t>
+          <t>Body5_Heading</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Body4_P1</t>
+          <t>Body5_P1</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>Body4_P2</t>
+          <t>Body5_P2</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
         <is>
-          <t>Body4_PerfectIf</t>
+          <t>Body6_Heading</t>
         </is>
       </c>
       <c r="R1" t="inlineStr">
         <is>
-          <t>Body5_Heading</t>
+          <t>Body6_P1</t>
         </is>
       </c>
       <c r="S1" t="inlineStr">
         <is>
-          <t>Body5_P1</t>
+          <t>Body6_P2</t>
         </is>
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Body5_P2</t>
+          <t>Body7_Heading</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>Body5_PerfectIf</t>
+          <t>Body7_P1</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
         <is>
-          <t>Body6_Heading</t>
+          <t>Body7_P2</t>
         </is>
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Body6_P1</t>
+          <t>Takeaway</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>Body6_P2</t>
+          <t>CTA_Question</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
-        <is>
-          <t>Body6_PerfectIf</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>Body7_Heading</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>Body7_P1</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>Body7_P2</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>Body7_PerfectIf</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>Takeaway</t>
-        </is>
-      </c>
-      <c r="AE1" t="inlineStr">
-        <is>
-          <t>CTA_Question</t>
-        </is>
-      </c>
-      <c r="AF1" t="inlineStr">
         <is>
           <t>CTA_Steps</t>
         </is>
@@ -601,140 +566,105 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>You feel overwhelmed trying to post everywhere</t>
+          <t>Step 2: Write a 3-Line Bio That Converts</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Step 2: Write a 3-Line Bio That Converts</t>
+          <t>Line one: who you help. Line two: how you help them. Line three: what to do next.</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Line one: who you help. Line two: how you help them. Line three: what to do next.</t>
+          <t>Drop the cute metaphors. Your bio should read like a clear signpost. Test it aloud — if a stranger wouldn't get it, rewrite.</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>Drop the cute metaphors. Your bio should read like a clear signpost. Test it aloud — if a stranger wouldn't get it, rewrite.</t>
+          <t>Step 3: Batch One Week of Content in 30 Minutes</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>Your bio sounds clever but nobody follows you from your profile</t>
+          <t>Set a timer for 30 minutes. Brain-dump 7 post ideas — one per day.</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Step 3: Batch One Week of Content in 30 Minutes</t>
+          <t>Pick your 3 strongest. Those become your posts. The rest become story ideas or future drafts.</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Set a timer for 30 minutes. Brain-dump 7 post ideas — one per day.</t>
+          <t>Step 4: Use the 80/20 Content Split</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Pick your 3 strongest. Those become your posts. The rest become story ideas or future drafts.</t>
+          <t>Eighty percent of your posts should give value — tips, stories, behind-the-scenes.</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>You stare at a blank screen every time you need to post</t>
+          <t>The other twenty percent can sell. People unfollow accounts that pitch every single post.</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>Step 4: Use the 80/20 Content Split</t>
+          <t>Step 5: Reply to 10 People Before You Post</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>Eighty percent of your posts should give value — tips, stories, behind-the-scenes.</t>
+          <t>Before you hit publish, spend 5 minutes leaving thoughtful replies on 10 posts in your niche.</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>The other twenty percent can sell. People unfollow accounts that pitch every single post.</t>
+          <t>Not love this — real replies that add something. This puts your name in front of new people before your post goes live.</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>You're not sure what to post without pitching your offer</t>
+          <t>Step 6: Pin Your Best-Performing Post</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>Step 5: Reply to 10 People Before You Post</t>
+          <t>Look at your analytics. Find the post with the most saves or shares — not just likes.</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>Before you hit publish, spend 5 minutes leaving thoughtful replies on 10 posts in your niche.</t>
+          <t>Pin it to the top of your profile. This becomes your silent salesperson while you sleep.</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>Not love this — real replies that add something. This puts your name in front of new people before your post goes live.</t>
+          <t>Step 7: End Every Post With a Micro-CTA</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>You post into the void and wonder why nobody sees your content</t>
+          <t>Don't just drop value and disappear. Every post needs one small ask — save this, share, comment.</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>Step 6: Pin Your Best-Performing Post</t>
+          <t>Micro-CTAs train your audience to interact. The more they engage, the more the platform shows your stuff.</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>Look at your analytics. Find the post with the most saves or shares — not just likes.</t>
+          <t>DO THIS FOR 4 WEEKS THEN CHECK YOUR INSIGHTS AND REPEAT WHAT WORKED</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Pin it to the top of your profile. This becomes your silent salesperson while you sleep.</t>
+          <t>Found this helpful?</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
-        <is>
-          <t>New visitors land on your profile and have no idea what you are about</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>Step 7: End Every Post With a Micro-CTA</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>Don't just drop value and disappear. Every post needs one small ask — save this, share, comment.</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>Micro-CTAs train your audience to interact. The more they engage, the more the platform shows your stuff.</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Your posts get views but zero comments</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>DO THIS FOR 4 WEEKS THEN CHECK YOUR INSIGHTS AND REPEAT WHAT WORKED</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>Found this helpful?</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
         <is>
           <t>1) SAVE FOR LATER
 2) COMMENT 'STRATEGY' TO GET MY FREE CONTENT STRATEGY GUIDE</t>
